--- a/health_tracking_forms/005_dietary_habits_and_frequency_survey--health_tracking_forms.xlsx
+++ b/health_tracking_forms/005_dietary_habits_and_frequency_survey--health_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Every day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'most_days'}</t>
+          <t>most_days</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Most days'}</t>
+          <t>Most days</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'grains'}</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Grains'}</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'proteins'}</t>
+          <t>proteins</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Proteins'}</t>
+          <t>Proteins</t>
         </is>
       </c>
     </row>
